--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t xml:space="preserve">Initial Testing</t>
   </si>
@@ -37,10 +37,142 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Visual Inspection</t>
+    <t xml:space="preserve">Test 1</t>
   </si>
   <si>
     <t xml:space="preserve">Is the workmanship acceptable for IPC Class II?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP1 and TP3 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP2 and TP3 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP4 and TP7 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP5 and TP7 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP6 and TP7 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP4 and TP5 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP4 and TP6 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP5 and TP6 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN2 Terminal 1 and Terminal 2 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN2 Terminal 1 and Terminal 2 ~= 120Ω?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP10 and TP13 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP11 and TP13 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP12 and TP13 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP10 and TP11 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN3 Terminal 1 and Terminal 4 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN3 Terminal 2 and Terminal 4 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN3 Terminal 3 and Terminal 4 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN3 Terminal 1 and Terminal 2 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN3 Terminal 1 and Terminal 3 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN3 Terminal 2 and Terminal 3 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 25</t>
   </si>
 </sst>
 </file>
@@ -50,11 +182,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -70,6 +203,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -127,24 +265,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -331,7 +473,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A6:R35"/>
+  <dimension ref="A6:R43"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -409,9 +551,13 @@
       <c r="R8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -429,15 +575,19 @@
       <c r="R9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="C10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -449,15 +599,19 @@
       <c r="R10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
+      <c r="A11" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="C11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -469,15 +623,19 @@
       <c r="R11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="C12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -489,15 +647,19 @@
       <c r="R12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
+      <c r="A13" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="C13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -509,15 +671,19 @@
       <c r="R13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="C14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -529,15 +695,19 @@
       <c r="R14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="C15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -549,15 +719,19 @@
       <c r="R15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3"/>
+      <c r="A16" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="C16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -569,15 +743,19 @@
       <c r="R16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="C17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -589,15 +767,19 @@
       <c r="R17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="C18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -609,15 +791,19 @@
       <c r="R18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="C19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -629,15 +815,19 @@
       <c r="R19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3"/>
+      <c r="A20" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="C20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -649,15 +839,19 @@
       <c r="R20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
+      <c r="A21" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="C21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -669,15 +863,19 @@
       <c r="R21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
+      <c r="A22" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="C22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -689,15 +887,19 @@
       <c r="R22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
+      <c r="A23" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="C23" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -709,15 +911,19 @@
       <c r="R23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3"/>
+      <c r="A24" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="C24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -729,15 +935,19 @@
       <c r="R24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="C25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -749,15 +959,19 @@
       <c r="R25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="C26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -769,15 +983,19 @@
       <c r="R26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3"/>
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="C27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -789,15 +1007,19 @@
       <c r="R27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
+      <c r="A28" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="C28" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -809,15 +1031,19 @@
       <c r="R28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3"/>
+      <c r="A29" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+      <c r="C29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -829,15 +1055,19 @@
       <c r="R29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3"/>
+      <c r="A30" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+      <c r="C30" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -849,7 +1079,9 @@
       <c r="R30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3"/>
+      <c r="A31" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -869,7 +1101,9 @@
       <c r="R31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3"/>
+      <c r="A32" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -948,8 +1182,168 @@
       <c r="Q35" s="4"/>
       <c r="R35" s="4"/>
     </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="88">
+  <mergeCells count="112">
     <mergeCell ref="A6:R6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:I7"/>
@@ -1038,6 +1432,30 @@
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="C35:I35"/>
     <mergeCell ref="K35:R35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="K36:R36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="K37:R37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:I38"/>
+    <mergeCell ref="K38:R38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:I39"/>
+    <mergeCell ref="K39:R39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:I40"/>
+    <mergeCell ref="K40:R40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:I41"/>
+    <mergeCell ref="K41:R41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C42:I42"/>
+    <mergeCell ref="K42:R42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:I43"/>
+    <mergeCell ref="K43:R43"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="99">
   <si>
     <t xml:space="preserve">Initial Testing</t>
   </si>
@@ -172,7 +172,151 @@
     <t xml:space="preserve">Test 24</t>
   </si>
   <si>
+    <t xml:space="preserve">Is the resistance between CN4 Terminal 1 and Terminal 4 &gt;= 1KΩ?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Test 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN4 Terminal 2 and Terminal 4 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN4 Terminal 3 and Terminal 4 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN4 Terminal 1 and Terminal 2 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN4 Terminal 1 and Terminal 3 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN4 Terminal 2 and Terminal 3 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP24 and TP25 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP22 and TP23 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP18 and TP19 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between TP20 and TP21 &gt;= 1KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN7 Terminal 1 and TP7 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN7 Terminal 2 and TP7 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN7 Terminal 3 and TP7 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN7 Terminal 4 and TP7 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN7 Terminal 1 and Terminal 4 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN7 Terminal 2 and Terminal 4 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN7 Terminal 3 and Terminal 4 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN7 Terminal 1 and Terminal 3 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN7 Terminal 2 and Terminal 3 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the resistance between CN7 Terminal 1 and Terminal 2 &gt;= 5KΩ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the PCB assembly pass the low voltage and limited current test?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the PCB assembly pass the operational voltage test?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the 3.3V power supply output the proper voltage within tolerance?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the 5.0V power supply output the proper voltage within tolerance?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 49</t>
   </si>
 </sst>
 </file>
@@ -473,7 +617,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A6:R43"/>
+  <dimension ref="A6:R57"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -579,15 +723,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -603,15 +747,15 @@
         <v>11</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -627,15 +771,15 @@
         <v>13</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -651,15 +795,15 @@
         <v>15</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -675,15 +819,15 @@
         <v>17</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -699,15 +843,15 @@
         <v>19</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -723,15 +867,15 @@
         <v>21</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -747,15 +891,15 @@
         <v>23</v>
       </c>
       <c r="B17" s="3"/>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -771,15 +915,15 @@
         <v>25</v>
       </c>
       <c r="B18" s="3"/>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -795,15 +939,15 @@
         <v>27</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -819,15 +963,15 @@
         <v>29</v>
       </c>
       <c r="B20" s="3"/>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -843,15 +987,15 @@
         <v>31</v>
       </c>
       <c r="B21" s="3"/>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -867,15 +1011,15 @@
         <v>33</v>
       </c>
       <c r="B22" s="3"/>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -891,15 +1035,15 @@
         <v>35</v>
       </c>
       <c r="B23" s="3"/>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -915,15 +1059,15 @@
         <v>36</v>
       </c>
       <c r="B24" s="3"/>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -939,15 +1083,15 @@
         <v>37</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -963,15 +1107,15 @@
         <v>39</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -987,15 +1131,15 @@
         <v>41</v>
       </c>
       <c r="B27" s="3"/>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1011,15 +1155,15 @@
         <v>43</v>
       </c>
       <c r="B28" s="3"/>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1035,15 +1179,15 @@
         <v>45</v>
       </c>
       <c r="B29" s="3"/>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1059,15 +1203,15 @@
         <v>47</v>
       </c>
       <c r="B30" s="3"/>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1083,7 +1227,9 @@
         <v>49</v>
       </c>
       <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="C31" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -1102,16 +1248,18 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="C32" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1123,15 +1271,19 @@
       <c r="R32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3"/>
+      <c r="A33" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="C33" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1143,15 +1295,19 @@
       <c r="R33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3"/>
+      <c r="A34" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="C34" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1163,15 +1319,19 @@
       <c r="R34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3"/>
+      <c r="A35" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="C35" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1183,15 +1343,19 @@
       <c r="R35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3"/>
+      <c r="A36" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+      <c r="C36" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1203,9 +1367,13 @@
       <c r="R36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3"/>
+      <c r="A37" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
+      <c r="C37" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -1223,9 +1391,13 @@
       <c r="R37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3"/>
+      <c r="A38" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
+      <c r="C38" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -1243,9 +1415,13 @@
       <c r="R38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3"/>
+      <c r="A39" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
+      <c r="C39" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -1263,9 +1439,13 @@
       <c r="R39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3"/>
+      <c r="A40" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
+      <c r="C40" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -1283,9 +1463,13 @@
       <c r="R40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3"/>
+      <c r="A41" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
+      <c r="C41" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -1303,9 +1487,13 @@
       <c r="R41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3"/>
+      <c r="A42" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
+      <c r="C42" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -1323,9 +1511,13 @@
       <c r="R42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3"/>
+      <c r="A43" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
+      <c r="C43" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -1342,8 +1534,336 @@
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
     </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="154">
     <mergeCell ref="A6:R6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:I7"/>
@@ -1456,6 +1976,48 @@
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="C43:I43"/>
     <mergeCell ref="K43:R43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="C44:I44"/>
+    <mergeCell ref="K44:R44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:I45"/>
+    <mergeCell ref="K45:R45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:I46"/>
+    <mergeCell ref="K46:R46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:I47"/>
+    <mergeCell ref="K47:R47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:I48"/>
+    <mergeCell ref="K48:R48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:I49"/>
+    <mergeCell ref="K49:R49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C50:I50"/>
+    <mergeCell ref="K50:R50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:I51"/>
+    <mergeCell ref="K51:R51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="K52:R52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C53:I53"/>
+    <mergeCell ref="K53:R53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:I54"/>
+    <mergeCell ref="K54:R54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:I55"/>
+    <mergeCell ref="K55:R55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:I56"/>
+    <mergeCell ref="K56:R56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="K57:R57"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
@@ -20,9 +20,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="99">
-  <si>
-    <t xml:space="preserve">Initial Testing</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="130">
+  <si>
+    <t xml:space="preserve">Functional Requirements Checklist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirement Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESP32 module with Wi‑Fi and BLE support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRV8825 driver with step/dir/enable interface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-24 V input with onboard 3.3 V and 5.0 V regulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pluggable headers for RS-485, motor outputs, limit inputs, and control inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USB programming interface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test points for power rails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEDs as visual indicators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial PCB Assembly Testing</t>
   </si>
   <si>
     <t xml:space="preserve">Test Item</t>
@@ -31,12 +88,6 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Test 1</t>
   </si>
   <si>
@@ -313,10 +364,52 @@
     <t xml:space="preserve">Does the 5.0V power supply output the proper voltage within tolerance?</t>
   </si>
   <si>
-    <t xml:space="preserve">Test 48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 49</t>
+    <t xml:space="preserve">Performance Requirements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor current output – Up to 2.5A loaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLE provisioning time - &lt; 10 s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB temperature rise - &lt; 40°C above ambient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firmware OTA success rate - &gt; 95%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage regulation ripple - &lt; 50mV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB Sub-System Testing and Verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the test computer recognize a newly connected serial port?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the basic HelloWorld firmware program and function properly?</t>
   </si>
 </sst>
 </file>
@@ -326,7 +419,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -347,11 +440,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -414,8 +502,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -430,8 +518,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -617,90 +705,66 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A6:R57"/>
+  <dimension ref="A7:R105"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="s">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -718,13 +782,13 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -742,13 +806,13 @@
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -766,13 +830,13 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -790,13 +854,13 @@
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -814,13 +878,13 @@
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -838,13 +902,13 @@
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -862,14 +926,10 @@
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>21</v>
-      </c>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3"/>
       <c r="B16" s="3"/>
-      <c r="C16" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -886,14 +946,10 @@
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>23</v>
-      </c>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -910,14 +966,10 @@
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>25</v>
-      </c>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3"/>
       <c r="B18" s="3"/>
-      <c r="C18" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -934,14 +986,10 @@
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>27</v>
-      </c>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3"/>
       <c r="B19" s="3"/>
-      <c r="C19" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -958,14 +1006,10 @@
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>29</v>
-      </c>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3"/>
       <c r="B20" s="3"/>
-      <c r="C20" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -982,14 +1026,10 @@
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>31</v>
-      </c>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3"/>
       <c r="B21" s="3"/>
-      <c r="C21" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -1006,14 +1046,10 @@
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>33</v>
-      </c>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
       <c r="B22" s="3"/>
-      <c r="C22" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -1030,14 +1066,10 @@
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>35</v>
-      </c>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3"/>
       <c r="B23" s="3"/>
-      <c r="C23" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -1054,14 +1086,10 @@
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>36</v>
-      </c>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3"/>
       <c r="B24" s="3"/>
-      <c r="C24" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -1078,14 +1106,10 @@
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3"/>
       <c r="B25" s="3"/>
-      <c r="C25" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1102,14 +1126,10 @@
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>39</v>
-      </c>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3"/>
       <c r="B26" s="3"/>
-      <c r="C26" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -1126,140 +1146,70 @@
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="4"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
-    </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
+      <c r="A30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
+      <c r="A31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="B32" s="3"/>
-      <c r="C32" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
+      <c r="C32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1272,18 +1222,18 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="B33" s="3"/>
-      <c r="C33" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
+      <c r="C33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1296,18 +1246,18 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B34" s="3"/>
-      <c r="C34" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
+      <c r="C34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1320,18 +1270,18 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="B35" s="3"/>
-      <c r="C35" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
+      <c r="C35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1342,20 +1292,20 @@
       <c r="Q35" s="4"/>
       <c r="R35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B36" s="3"/>
-      <c r="C36" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
+      <c r="C36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1366,13 +1316,13 @@
       <c r="Q36" s="4"/>
       <c r="R36" s="4"/>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -1390,13 +1340,13 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -1414,13 +1364,13 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -1438,13 +1388,13 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -1462,13 +1412,13 @@
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -1486,13 +1436,13 @@
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="3" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -1510,13 +1460,13 @@
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -1534,13 +1484,13 @@
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -1558,13 +1508,13 @@
       <c r="Q44" s="4"/>
       <c r="R44" s="4"/>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -1582,13 +1532,13 @@
       <c r="Q45" s="4"/>
       <c r="R45" s="4"/>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -1606,13 +1556,13 @@
       <c r="Q46" s="4"/>
       <c r="R46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -1630,13 +1580,13 @@
       <c r="Q47" s="4"/>
       <c r="R47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -1654,13 +1604,13 @@
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -1678,13 +1628,13 @@
       <c r="Q49" s="4"/>
       <c r="R49" s="4"/>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -1702,13 +1652,13 @@
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -1726,13 +1676,13 @@
       <c r="Q51" s="4"/>
       <c r="R51" s="4"/>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -1750,13 +1700,13 @@
       <c r="Q52" s="4"/>
       <c r="R52" s="4"/>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -1774,13 +1724,13 @@
       <c r="Q53" s="4"/>
       <c r="R53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -1798,12 +1748,14 @@
       <c r="Q54" s="4"/>
       <c r="R54" s="4"/>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
+      <c r="C55" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -1820,12 +1772,14 @@
       <c r="Q55" s="4"/>
       <c r="R55" s="4"/>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
+      <c r="C56" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -1842,10 +1796,14 @@
       <c r="Q56" s="4"/>
       <c r="R56" s="4"/>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3"/>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
+      <c r="C57" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -1862,12 +1820,1021 @@
       <c r="Q57" s="4"/>
       <c r="R57" s="4"/>
     </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="4"/>
+      <c r="R73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4"/>
+      <c r="R74" s="4"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="4"/>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="4"/>
+      <c r="Q80" s="4"/>
+      <c r="R80" s="4"/>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4"/>
+      <c r="Q81" s="4"/>
+      <c r="R81" s="4"/>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
+      <c r="L84" s="5"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="5"/>
+      <c r="Q84" s="5"/>
+      <c r="R84" s="5"/>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="2"/>
+      <c r="R85" s="2"/>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4"/>
+      <c r="P86" s="4"/>
+      <c r="Q86" s="4"/>
+      <c r="R86" s="4"/>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="4"/>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="4"/>
+      <c r="Q87" s="4"/>
+      <c r="R87" s="4"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4"/>
+      <c r="P88" s="4"/>
+      <c r="Q88" s="4"/>
+      <c r="R88" s="4"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="4"/>
+      <c r="N89" s="4"/>
+      <c r="O89" s="4"/>
+      <c r="P89" s="4"/>
+      <c r="Q89" s="4"/>
+      <c r="R89" s="4"/>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4"/>
+      <c r="P90" s="4"/>
+      <c r="Q90" s="4"/>
+      <c r="R90" s="4"/>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="4"/>
+      <c r="Q91" s="4"/>
+      <c r="R91" s="4"/>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+      <c r="O92" s="4"/>
+      <c r="P92" s="4"/>
+      <c r="Q92" s="4"/>
+      <c r="R92" s="4"/>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
+      <c r="N93" s="4"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="4"/>
+      <c r="Q93" s="4"/>
+      <c r="R93" s="4"/>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="4"/>
+      <c r="Q94" s="4"/>
+      <c r="R94" s="4"/>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4"/>
+      <c r="Q95" s="4"/>
+      <c r="R95" s="4"/>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+      <c r="O96" s="4"/>
+      <c r="P96" s="4"/>
+      <c r="Q96" s="4"/>
+      <c r="R96" s="4"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4"/>
+      <c r="N97" s="4"/>
+      <c r="O97" s="4"/>
+      <c r="P97" s="4"/>
+      <c r="Q97" s="4"/>
+      <c r="R97" s="4"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+      <c r="K100" s="5"/>
+      <c r="L100" s="5"/>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5"/>
+      <c r="O100" s="5"/>
+      <c r="P100" s="5"/>
+      <c r="Q100" s="5"/>
+      <c r="R100" s="5"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="2"/>
+      <c r="M101" s="2"/>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" s="2"/>
+      <c r="Q101" s="2"/>
+      <c r="R101" s="2"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="4"/>
+      <c r="R102" s="4"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="4"/>
+      <c r="R103" s="4"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="4"/>
+      <c r="R104" s="4"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="4"/>
+      <c r="Q105" s="4"/>
+      <c r="R105" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="154">
-    <mergeCell ref="A6:R6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="K7:R7"/>
+  <mergeCells count="268">
+    <mergeCell ref="A7:R7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="K8:R8"/>
@@ -1925,18 +2892,7 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="C26:I26"/>
     <mergeCell ref="K26:R26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="K27:R27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="K28:R28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:I29"/>
-    <mergeCell ref="K29:R29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:I30"/>
-    <mergeCell ref="K30:R30"/>
+    <mergeCell ref="A30:R30"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="K31:R31"/>
@@ -2018,6 +2974,134 @@
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="C57:I57"/>
     <mergeCell ref="K57:R57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="C58:I58"/>
+    <mergeCell ref="K58:R58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:I59"/>
+    <mergeCell ref="K59:R59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:I60"/>
+    <mergeCell ref="K60:R60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C61:I61"/>
+    <mergeCell ref="K61:R61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:I62"/>
+    <mergeCell ref="K62:R62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C63:I63"/>
+    <mergeCell ref="K63:R63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:I64"/>
+    <mergeCell ref="K64:R64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:I65"/>
+    <mergeCell ref="K65:R65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C66:I66"/>
+    <mergeCell ref="K66:R66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="K67:R67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:I68"/>
+    <mergeCell ref="K68:R68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:I69"/>
+    <mergeCell ref="K69:R69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:I70"/>
+    <mergeCell ref="K70:R70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:I71"/>
+    <mergeCell ref="K71:R71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:I72"/>
+    <mergeCell ref="K72:R72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:I73"/>
+    <mergeCell ref="K73:R73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:I74"/>
+    <mergeCell ref="K74:R74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:I75"/>
+    <mergeCell ref="K75:R75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="K76:R76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:I77"/>
+    <mergeCell ref="K77:R77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:I78"/>
+    <mergeCell ref="K78:R78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:I79"/>
+    <mergeCell ref="K79:R79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:I80"/>
+    <mergeCell ref="K80:R80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="K81:R81"/>
+    <mergeCell ref="A84:R84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="C85:I85"/>
+    <mergeCell ref="K85:R85"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="C86:I86"/>
+    <mergeCell ref="K86:R86"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="C87:I87"/>
+    <mergeCell ref="K87:R87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C88:I88"/>
+    <mergeCell ref="K88:R88"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="C89:I89"/>
+    <mergeCell ref="K89:R89"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:I90"/>
+    <mergeCell ref="K90:R90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:I91"/>
+    <mergeCell ref="K91:R91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:I92"/>
+    <mergeCell ref="K92:R92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:I93"/>
+    <mergeCell ref="K93:R93"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:I94"/>
+    <mergeCell ref="K94:R94"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:I95"/>
+    <mergeCell ref="K95:R95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:I96"/>
+    <mergeCell ref="K96:R96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:I97"/>
+    <mergeCell ref="K97:R97"/>
+    <mergeCell ref="A100:R100"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="C101:I101"/>
+    <mergeCell ref="K101:R101"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="C102:I102"/>
+    <mergeCell ref="K102:R102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:I103"/>
+    <mergeCell ref="K103:R103"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="C104:I104"/>
+    <mergeCell ref="K104:R104"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="C105:I105"/>
+    <mergeCell ref="K105:R105"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="148">
   <si>
     <t xml:space="preserve">Functional Requirements Checklist</t>
   </si>
@@ -410,6 +410,60 @@
   </si>
   <si>
     <t xml:space="preserve">Does the basic HelloWorld firmware program and function properly?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the UARTFTDI firmware and interface operate properly?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the red status LED flash at the proper rate?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the RS-485 interface function properly?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the input for CN3 terminal 1 operate properly?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the input for CN3 terminal 2 operate properly?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the input for CN3 terminal 3 operate properly?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the input for CN4 terminal 1 operate properly?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the input for CN4 terminal 2 operate properly?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the input for CN4 terminal 3 operate properly?</t>
   </si>
 </sst>
 </file>
@@ -419,7 +473,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -440,6 +494,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -497,12 +556,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -520,6 +579,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -705,7 +768,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A7:R105"/>
+  <dimension ref="A7:R114"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2793,9 +2856,13 @@
       <c r="R103" s="4"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="3"/>
+      <c r="A104" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
+      <c r="C104" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
@@ -2813,9 +2880,13 @@
       <c r="R104" s="4"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="3"/>
+      <c r="A105" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
+      <c r="C105" s="3" t="s">
+        <v>133</v>
+      </c>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
@@ -2832,8 +2903,216 @@
       <c r="Q105" s="4"/>
       <c r="R105" s="4"/>
     </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4"/>
+      <c r="Q106" s="4"/>
+      <c r="R106" s="4"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="4"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="4"/>
+      <c r="R108" s="4"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B109" s="3"/>
+      <c r="C109" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
+      <c r="Q109" s="4"/>
+      <c r="R109" s="4"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B110" s="3"/>
+      <c r="C110" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="6"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="4"/>
+      <c r="R110" s="4"/>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B111" s="3"/>
+      <c r="C111" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D111" s="6"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="6"/>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4"/>
+      <c r="O111" s="4"/>
+      <c r="P111" s="4"/>
+      <c r="Q111" s="4"/>
+      <c r="R111" s="4"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B112" s="3"/>
+      <c r="C112" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4"/>
+      <c r="P112" s="4"/>
+      <c r="Q112" s="4"/>
+      <c r="R112" s="4"/>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="3"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="4"/>
+      <c r="R113" s="4"/>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+      <c r="P114" s="4"/>
+      <c r="Q114" s="4"/>
+      <c r="R114" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="268">
+  <mergeCells count="295">
     <mergeCell ref="A7:R7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:I8"/>
@@ -3102,6 +3381,33 @@
     <mergeCell ref="A105:B105"/>
     <mergeCell ref="C105:I105"/>
     <mergeCell ref="K105:R105"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="C106:I106"/>
+    <mergeCell ref="K106:R106"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="C107:I107"/>
+    <mergeCell ref="K107:R107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:I108"/>
+    <mergeCell ref="K108:R108"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:I109"/>
+    <mergeCell ref="K109:R109"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="C110:I110"/>
+    <mergeCell ref="K110:R110"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="C111:I111"/>
+    <mergeCell ref="K111:R111"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="C112:I112"/>
+    <mergeCell ref="K112:R112"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:I113"/>
+    <mergeCell ref="K113:R113"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="C114:I114"/>
+    <mergeCell ref="K114:R114"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="152">
   <si>
     <t xml:space="preserve">Functional Requirements Checklist</t>
   </si>
@@ -464,6 +464,18 @@
   </si>
   <si>
     <t xml:space="preserve">Does the input for CN4 terminal 3 operate properly?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do the inputs operate properly using a PLC as a control source?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SST 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does the stepper motor driver IC operate properly?</t>
   </si>
 </sst>
 </file>
@@ -473,7 +485,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -494,11 +506,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -556,7 +563,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -579,10 +586,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2980,15 +2983,15 @@
         <v>140</v>
       </c>
       <c r="B109" s="3"/>
-      <c r="C109" s="6" t="s">
+      <c r="C109" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
@@ -3004,15 +3007,15 @@
         <v>142</v>
       </c>
       <c r="B110" s="3"/>
-      <c r="C110" s="6" t="s">
+      <c r="C110" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
@@ -3028,15 +3031,15 @@
         <v>144</v>
       </c>
       <c r="B111" s="3"/>
-      <c r="C111" s="6" t="s">
+      <c r="C111" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D111" s="6"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
@@ -3052,15 +3055,15 @@
         <v>146</v>
       </c>
       <c r="B112" s="3"/>
-      <c r="C112" s="6" t="s">
+      <c r="C112" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D112" s="6"/>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3"/>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
       <c r="L112" s="4"/>
@@ -3072,9 +3075,13 @@
       <c r="R112" s="4"/>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="3"/>
+      <c r="A113" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
+      <c r="C113" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
@@ -3092,9 +3099,13 @@
       <c r="R113" s="4"/>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="3"/>
+      <c r="A114" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
+      <c r="C114" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="172">
   <si>
     <t xml:space="preserve">Project ID Number:</t>
   </si>
@@ -40,6 +40,9 @@
     <t xml:space="preserve">Tested By:</t>
   </si>
   <si>
+    <t xml:space="preserve">MSD</t>
+  </si>
+  <si>
     <t xml:space="preserve">Test Date:</t>
   </si>
   <si>
@@ -70,6 +73,33 @@
     <t xml:space="preserve">Next Calibration Date</t>
   </si>
   <si>
+    <t xml:space="preserve">Handheld DMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agilent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U1252B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MY52100005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bench Power Supply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPE6102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPE610224121294</t>
+  </si>
+  <si>
     <t xml:space="preserve">Functional Requirements Checklist</t>
   </si>
   <si>
@@ -89,6 +119,9 @@
   </si>
   <si>
     <t xml:space="preserve">ESP32 module with Wi‑Fi and BLE support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass</t>
   </si>
   <si>
     <t xml:space="preserve">FR-002</t>
@@ -509,10 +542,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -537,13 +571,6 @@
     <font>
       <b val="true"/>
       <sz val="20"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -604,7 +631,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -625,6 +652,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -637,7 +668,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -651,18 +682,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -936,7 +955,9 @@
         <v>5</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -955,11 +976,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="C5" s="5" t="n">
+        <v>45662</v>
+      </c>
+      <c r="D5" s="5"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -977,7 +1000,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
@@ -997,447 +1020,439 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-    </row>
-    <row r="8" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-    </row>
-    <row r="9" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-    </row>
-    <row r="10" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+    <row r="7" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+    </row>
+    <row r="8" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+    </row>
+    <row r="9" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+    </row>
+    <row r="10" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11" t="s">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11" t="s">
+      <c r="D10" s="11"/>
+      <c r="E10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11" t="s">
+      <c r="F10" s="12"/>
+      <c r="G10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11" t="s">
+      <c r="H10" s="12"/>
+      <c r="I10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11" t="s">
+      <c r="J10" s="12"/>
+      <c r="K10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-    </row>
-    <row r="11" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+    </row>
+    <row r="11" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="12" t="s">
+        <v>19</v>
+      </c>
       <c r="F11" s="12"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-    </row>
-    <row r="12" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="12"/>
+      <c r="G11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+    </row>
+    <row r="12" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="F12" s="12"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-    </row>
-    <row r="13" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+      <c r="G12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+    </row>
+    <row r="13" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-    </row>
-    <row r="14" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+    </row>
+    <row r="14" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-    </row>
-    <row r="15" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+    </row>
+    <row r="15" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-    </row>
-    <row r="16" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+    </row>
+    <row r="16" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-    </row>
-    <row r="17" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+    </row>
+    <row r="17" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-    </row>
-    <row r="18" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+    </row>
+    <row r="18" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-    </row>
-    <row r="19" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+    </row>
+    <row r="19" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-    </row>
-    <row r="20" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+    </row>
+    <row r="20" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-    </row>
-    <row r="21" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+    </row>
+    <row r="21" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
-    </row>
-    <row r="22" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+    </row>
+    <row r="22" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
-    </row>
-    <row r="23" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0"/>
-      <c r="B23" s="0"/>
-      <c r="C23" s="0"/>
-      <c r="D23" s="0"/>
-      <c r="E23" s="0"/>
-      <c r="F23" s="0"/>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
-      <c r="I23" s="0"/>
-      <c r="J23" s="0"/>
-      <c r="K23" s="0"/>
-      <c r="L23" s="0"/>
-      <c r="M23" s="0"/>
-      <c r="N23" s="0"/>
-      <c r="O23" s="0"/>
-      <c r="P23" s="0"/>
-      <c r="Q23" s="0"/>
-      <c r="R23" s="0"/>
-    </row>
-    <row r="24" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0"/>
-      <c r="B24" s="0"/>
-      <c r="C24" s="0"/>
-      <c r="D24" s="0"/>
-      <c r="E24" s="0"/>
-      <c r="F24" s="0"/>
-      <c r="G24" s="0"/>
-      <c r="H24" s="0"/>
-      <c r="I24" s="0"/>
-      <c r="J24" s="0"/>
-      <c r="K24" s="0"/>
-      <c r="L24" s="0"/>
-      <c r="M24" s="0"/>
-      <c r="N24" s="0"/>
-      <c r="O24" s="0"/>
-      <c r="P24" s="0"/>
-      <c r="Q24" s="0"/>
-      <c r="R24" s="0"/>
-    </row>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+    </row>
+    <row r="23" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
+      <c r="A25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K26" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
+      <c r="A26" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="4"/>
+      <c r="A27" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -1448,20 +1463,22 @@
       <c r="R27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="4"/>
+      <c r="A28" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -1472,20 +1489,22 @@
       <c r="R28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="4"/>
+      <c r="A29" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -1496,20 +1515,22 @@
       <c r="R29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="4"/>
+      <c r="A30" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -1520,20 +1541,22 @@
       <c r="R30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="4"/>
+      <c r="A31" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -1544,20 +1567,22 @@
       <c r="R31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="4"/>
+      <c r="A32" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -1568,20 +1593,22 @@
       <c r="R32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="4"/>
+      <c r="A33" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -1592,70 +1619,72 @@
       <c r="R33" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
+      <c r="A36" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="14"/>
+      <c r="Q36" s="14"/>
+      <c r="R36" s="14"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="14"/>
+      <c r="A37" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="11"/>
+      <c r="R37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="4"/>
+      <c r="A38" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
@@ -1666,20 +1695,22 @@
       <c r="R38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="4"/>
+      <c r="A39" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
@@ -1690,20 +1721,22 @@
       <c r="R39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="4"/>
+      <c r="A40" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
@@ -1714,20 +1747,22 @@
       <c r="R40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="4"/>
+      <c r="A41" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
@@ -1738,20 +1773,22 @@
       <c r="R41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="4"/>
+      <c r="A42" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
@@ -1762,20 +1799,22 @@
       <c r="R42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="4"/>
+      <c r="A43" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
@@ -1786,20 +1825,22 @@
       <c r="R43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="4"/>
+      <c r="A44" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
@@ -1810,20 +1851,22 @@
       <c r="R44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="4"/>
+      <c r="A45" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
@@ -1834,20 +1877,22 @@
       <c r="R45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="4"/>
+      <c r="A46" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
@@ -1858,20 +1903,22 @@
       <c r="R46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="4"/>
+      <c r="A47" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
@@ -1882,20 +1929,22 @@
       <c r="R47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="4"/>
+      <c r="A48" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
@@ -1906,20 +1955,22 @@
       <c r="R48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="4"/>
+      <c r="A49" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
@@ -1930,20 +1981,22 @@
       <c r="R49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="4"/>
+      <c r="A50" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
@@ -1954,20 +2007,22 @@
       <c r="R50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="4"/>
+      <c r="A51" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
@@ -1978,20 +2033,22 @@
       <c r="R51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="4"/>
+      <c r="A52" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
@@ -2002,20 +2059,22 @@
       <c r="R52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="4"/>
+      <c r="A53" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
@@ -2026,20 +2085,22 @@
       <c r="R53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="4"/>
+      <c r="A54" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
@@ -2050,20 +2111,22 @@
       <c r="R54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="4"/>
+      <c r="A55" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
@@ -2074,20 +2137,22 @@
       <c r="R55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="4"/>
+      <c r="A56" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
@@ -2098,20 +2163,22 @@
       <c r="R56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="4"/>
+      <c r="A57" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
@@ -2122,20 +2189,22 @@
       <c r="R57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="4"/>
+      <c r="A58" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
@@ -2146,20 +2215,22 @@
       <c r="R58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="4"/>
+      <c r="A59" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
@@ -2170,20 +2241,22 @@
       <c r="R59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="4"/>
+      <c r="A60" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
@@ -2194,20 +2267,22 @@
       <c r="R60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="15"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="4"/>
+      <c r="A61" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
@@ -2218,20 +2293,22 @@
       <c r="R61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B62" s="15"/>
-      <c r="C62" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="15"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="4"/>
+      <c r="A62" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
@@ -2242,20 +2319,22 @@
       <c r="R62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="4"/>
+      <c r="A63" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
@@ -2266,20 +2345,22 @@
       <c r="R63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B64" s="15"/>
-      <c r="C64" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="4"/>
+      <c r="A64" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
@@ -2290,20 +2371,22 @@
       <c r="R64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B65" s="15"/>
-      <c r="C65" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="4"/>
+      <c r="A65" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
@@ -2314,20 +2397,22 @@
       <c r="R65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B66" s="15"/>
-      <c r="C66" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="4"/>
+      <c r="A66" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
@@ -2338,20 +2423,22 @@
       <c r="R66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B67" s="15"/>
-      <c r="C67" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D67" s="15"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="4"/>
+      <c r="A67" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
@@ -2362,20 +2449,22 @@
       <c r="R67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="B68" s="15"/>
-      <c r="C68" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="4"/>
+      <c r="A68" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
@@ -2386,20 +2475,22 @@
       <c r="R68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B69" s="15"/>
-      <c r="C69" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D69" s="15"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="4"/>
+      <c r="A69" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
@@ -2410,20 +2501,22 @@
       <c r="R69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="15"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="4"/>
+      <c r="A70" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
@@ -2434,20 +2527,22 @@
       <c r="R70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="15"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="4"/>
+      <c r="A71" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B71" s="13"/>
+      <c r="C71" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D71" s="13"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
@@ -2458,20 +2553,22 @@
       <c r="R71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="B72" s="15"/>
-      <c r="C72" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="15"/>
-      <c r="H72" s="15"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="4"/>
+      <c r="A72" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B72" s="13"/>
+      <c r="C72" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D72" s="13"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
@@ -2482,20 +2579,22 @@
       <c r="R72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B73" s="15"/>
-      <c r="C73" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="15"/>
-      <c r="H73" s="15"/>
-      <c r="I73" s="15"/>
-      <c r="J73" s="4"/>
+      <c r="A73" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B73" s="13"/>
+      <c r="C73" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D73" s="13"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
@@ -2506,20 +2605,22 @@
       <c r="R73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B74" s="15"/>
-      <c r="C74" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="15"/>
-      <c r="H74" s="15"/>
-      <c r="I74" s="15"/>
-      <c r="J74" s="4"/>
+      <c r="A74" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B74" s="13"/>
+      <c r="C74" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
@@ -2530,20 +2631,22 @@
       <c r="R74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B75" s="15"/>
-      <c r="C75" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D75" s="15"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
-      <c r="G75" s="15"/>
-      <c r="H75" s="15"/>
-      <c r="I75" s="15"/>
-      <c r="J75" s="4"/>
+      <c r="A75" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
@@ -2554,20 +2657,22 @@
       <c r="R75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B76" s="15"/>
-      <c r="C76" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="15"/>
-      <c r="H76" s="15"/>
-      <c r="I76" s="15"/>
-      <c r="J76" s="4"/>
+      <c r="A76" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B76" s="13"/>
+      <c r="C76" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K76" s="4"/>
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
@@ -2578,20 +2683,22 @@
       <c r="R76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B77" s="15"/>
-      <c r="C77" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="4"/>
+      <c r="A77" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K77" s="4"/>
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
@@ -2602,20 +2709,22 @@
       <c r="R77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="B78" s="15"/>
-      <c r="C78" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="15"/>
-      <c r="H78" s="15"/>
-      <c r="I78" s="15"/>
-      <c r="J78" s="4"/>
+      <c r="A78" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B78" s="13"/>
+      <c r="C78" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K78" s="4"/>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
@@ -2626,20 +2735,22 @@
       <c r="R78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
-      <c r="H79" s="15"/>
-      <c r="I79" s="15"/>
-      <c r="J79" s="4"/>
+      <c r="A79" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B79" s="13"/>
+      <c r="C79" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
@@ -2650,20 +2761,22 @@
       <c r="R79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B80" s="15"/>
-      <c r="C80" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="15"/>
-      <c r="H80" s="15"/>
-      <c r="I80" s="15"/>
-      <c r="J80" s="4"/>
+      <c r="A80" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B80" s="13"/>
+      <c r="C80" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
+      <c r="J80" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
@@ -2674,20 +2787,22 @@
       <c r="R80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B81" s="15"/>
-      <c r="C81" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="D81" s="15"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="15"/>
-      <c r="G81" s="15"/>
-      <c r="H81" s="15"/>
-      <c r="I81" s="15"/>
-      <c r="J81" s="4"/>
+      <c r="A81" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B81" s="13"/>
+      <c r="C81" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="13"/>
+      <c r="J81" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
@@ -2698,20 +2813,22 @@
       <c r="R81" s="4"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B82" s="15"/>
-      <c r="C82" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15"/>
-      <c r="H82" s="15"/>
-      <c r="I82" s="15"/>
-      <c r="J82" s="4"/>
+      <c r="A82" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="13"/>
+      <c r="J82" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K82" s="4"/>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
@@ -2722,20 +2839,22 @@
       <c r="R82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="B83" s="15"/>
-      <c r="C83" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D83" s="15"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="15"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="15"/>
-      <c r="I83" s="15"/>
-      <c r="J83" s="4"/>
+      <c r="A83" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="13"/>
+      <c r="I83" s="13"/>
+      <c r="J83" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K83" s="4"/>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
@@ -2746,20 +2865,22 @@
       <c r="R83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B84" s="15"/>
-      <c r="C84" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D84" s="15"/>
-      <c r="E84" s="15"/>
-      <c r="F84" s="15"/>
-      <c r="G84" s="15"/>
-      <c r="H84" s="15"/>
-      <c r="I84" s="15"/>
-      <c r="J84" s="4"/>
+      <c r="A84" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B84" s="13"/>
+      <c r="C84" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="13"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="13"/>
+      <c r="J84" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
@@ -2770,70 +2891,72 @@
       <c r="R84" s="4"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="B87" s="16"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="16"/>
-      <c r="E87" s="16"/>
-      <c r="F87" s="16"/>
-      <c r="G87" s="16"/>
-      <c r="H87" s="16"/>
-      <c r="I87" s="16"/>
-      <c r="J87" s="16"/>
-      <c r="K87" s="16"/>
-      <c r="L87" s="16"/>
-      <c r="M87" s="16"/>
-      <c r="N87" s="16"/>
-      <c r="O87" s="16"/>
-      <c r="P87" s="16"/>
-      <c r="Q87" s="16"/>
-      <c r="R87" s="16"/>
+      <c r="A87" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+      <c r="K87" s="14"/>
+      <c r="L87" s="14"/>
+      <c r="M87" s="14"/>
+      <c r="N87" s="14"/>
+      <c r="O87" s="14"/>
+      <c r="P87" s="14"/>
+      <c r="Q87" s="14"/>
+      <c r="R87" s="14"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B88" s="14"/>
-      <c r="C88" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="H88" s="14"/>
-      <c r="I88" s="14"/>
-      <c r="J88" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K88" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L88" s="14"/>
-      <c r="M88" s="14"/>
-      <c r="N88" s="14"/>
-      <c r="O88" s="14"/>
-      <c r="P88" s="14"/>
-      <c r="Q88" s="14"/>
-      <c r="R88" s="14"/>
+      <c r="A88" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="11"/>
+      <c r="I88" s="11"/>
+      <c r="J88" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K88" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L88" s="11"/>
+      <c r="M88" s="11"/>
+      <c r="N88" s="11"/>
+      <c r="O88" s="11"/>
+      <c r="P88" s="11"/>
+      <c r="Q88" s="11"/>
+      <c r="R88" s="11"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B89" s="15"/>
-      <c r="C89" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="D89" s="15"/>
-      <c r="E89" s="15"/>
-      <c r="F89" s="15"/>
-      <c r="G89" s="15"/>
-      <c r="H89" s="15"/>
-      <c r="I89" s="15"/>
-      <c r="J89" s="4"/>
+      <c r="A89" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B89" s="13"/>
+      <c r="C89" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="13"/>
+      <c r="G89" s="13"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13"/>
+      <c r="J89" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K89" s="4"/>
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
@@ -2844,20 +2967,20 @@
       <c r="R89" s="4"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B90" s="15"/>
-      <c r="C90" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="D90" s="15"/>
-      <c r="E90" s="15"/>
-      <c r="F90" s="15"/>
-      <c r="G90" s="15"/>
-      <c r="H90" s="15"/>
-      <c r="I90" s="15"/>
-      <c r="J90" s="4"/>
+      <c r="A90" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B90" s="13"/>
+      <c r="C90" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="13"/>
       <c r="K90" s="4"/>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
@@ -2868,20 +2991,20 @@
       <c r="R90" s="4"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="B91" s="15"/>
-      <c r="C91" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D91" s="15"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="15"/>
-      <c r="G91" s="15"/>
-      <c r="H91" s="15"/>
-      <c r="I91" s="15"/>
-      <c r="J91" s="4"/>
+      <c r="A91" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B91" s="13"/>
+      <c r="C91" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="13"/>
+      <c r="H91" s="13"/>
+      <c r="I91" s="13"/>
+      <c r="J91" s="13"/>
       <c r="K91" s="4"/>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
@@ -2892,20 +3015,20 @@
       <c r="R91" s="4"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="B92" s="15"/>
-      <c r="C92" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
-      <c r="H92" s="15"/>
-      <c r="I92" s="15"/>
-      <c r="J92" s="4"/>
+      <c r="A92" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B92" s="13"/>
+      <c r="C92" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D92" s="13"/>
+      <c r="E92" s="13"/>
+      <c r="F92" s="13"/>
+      <c r="G92" s="13"/>
+      <c r="H92" s="13"/>
+      <c r="I92" s="13"/>
+      <c r="J92" s="13"/>
       <c r="K92" s="4"/>
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
@@ -2916,20 +3039,20 @@
       <c r="R92" s="4"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="B93" s="15"/>
-      <c r="C93" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="D93" s="15"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15"/>
-      <c r="H93" s="15"/>
-      <c r="I93" s="15"/>
-      <c r="J93" s="4"/>
+      <c r="A93" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B93" s="13"/>
+      <c r="C93" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="13"/>
+      <c r="J93" s="13"/>
       <c r="K93" s="4"/>
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
@@ -2940,20 +3063,20 @@
       <c r="R93" s="4"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B94" s="15"/>
-      <c r="C94" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D94" s="15"/>
-      <c r="E94" s="15"/>
-      <c r="F94" s="15"/>
-      <c r="G94" s="15"/>
-      <c r="H94" s="15"/>
-      <c r="I94" s="15"/>
-      <c r="J94" s="4"/>
+      <c r="A94" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B94" s="13"/>
+      <c r="C94" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="13"/>
+      <c r="H94" s="13"/>
+      <c r="I94" s="13"/>
+      <c r="J94" s="13"/>
       <c r="K94" s="4"/>
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
@@ -2964,20 +3087,20 @@
       <c r="R94" s="4"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="B95" s="15"/>
-      <c r="C95" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D95" s="15"/>
-      <c r="E95" s="15"/>
-      <c r="F95" s="15"/>
-      <c r="G95" s="15"/>
-      <c r="H95" s="15"/>
-      <c r="I95" s="15"/>
-      <c r="J95" s="4"/>
+      <c r="A95" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B95" s="13"/>
+      <c r="C95" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="D95" s="13"/>
+      <c r="E95" s="13"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="13"/>
+      <c r="H95" s="13"/>
+      <c r="I95" s="13"/>
+      <c r="J95" s="13"/>
       <c r="K95" s="4"/>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
@@ -2988,20 +3111,20 @@
       <c r="R95" s="4"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B96" s="15"/>
-      <c r="C96" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D96" s="15"/>
-      <c r="E96" s="15"/>
-      <c r="F96" s="15"/>
-      <c r="G96" s="15"/>
-      <c r="H96" s="15"/>
-      <c r="I96" s="15"/>
-      <c r="J96" s="4"/>
+      <c r="A96" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B96" s="13"/>
+      <c r="C96" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="D96" s="13"/>
+      <c r="E96" s="13"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13"/>
+      <c r="I96" s="13"/>
+      <c r="J96" s="13"/>
       <c r="K96" s="4"/>
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
@@ -3012,20 +3135,20 @@
       <c r="R96" s="4"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="B97" s="15"/>
-      <c r="C97" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="D97" s="15"/>
-      <c r="E97" s="15"/>
-      <c r="F97" s="15"/>
-      <c r="G97" s="15"/>
-      <c r="H97" s="15"/>
-      <c r="I97" s="15"/>
-      <c r="J97" s="4"/>
+      <c r="A97" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B97" s="13"/>
+      <c r="C97" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D97" s="13"/>
+      <c r="E97" s="13"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="13"/>
+      <c r="H97" s="13"/>
+      <c r="I97" s="13"/>
+      <c r="J97" s="13"/>
       <c r="K97" s="4"/>
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
@@ -3036,20 +3159,20 @@
       <c r="R97" s="4"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B98" s="15"/>
-      <c r="C98" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="D98" s="15"/>
-      <c r="E98" s="15"/>
-      <c r="F98" s="15"/>
-      <c r="G98" s="15"/>
-      <c r="H98" s="15"/>
-      <c r="I98" s="15"/>
-      <c r="J98" s="4"/>
+      <c r="A98" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B98" s="13"/>
+      <c r="C98" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D98" s="13"/>
+      <c r="E98" s="13"/>
+      <c r="F98" s="13"/>
+      <c r="G98" s="13"/>
+      <c r="H98" s="13"/>
+      <c r="I98" s="13"/>
+      <c r="J98" s="13"/>
       <c r="K98" s="4"/>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
@@ -3060,20 +3183,20 @@
       <c r="R98" s="4"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="B99" s="15"/>
-      <c r="C99" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="D99" s="15"/>
-      <c r="E99" s="15"/>
-      <c r="F99" s="15"/>
-      <c r="G99" s="15"/>
-      <c r="H99" s="15"/>
-      <c r="I99" s="15"/>
-      <c r="J99" s="4"/>
+      <c r="A99" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B99" s="13"/>
+      <c r="C99" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13"/>
+      <c r="H99" s="13"/>
+      <c r="I99" s="13"/>
+      <c r="J99" s="13"/>
       <c r="K99" s="4"/>
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
@@ -3084,20 +3207,20 @@
       <c r="R99" s="4"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="B100" s="15"/>
-      <c r="C100" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="D100" s="15"/>
-      <c r="E100" s="15"/>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15"/>
-      <c r="H100" s="15"/>
-      <c r="I100" s="15"/>
-      <c r="J100" s="4"/>
+      <c r="A100" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B100" s="13"/>
+      <c r="C100" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13"/>
+      <c r="G100" s="13"/>
+      <c r="H100" s="13"/>
+      <c r="I100" s="13"/>
+      <c r="J100" s="13"/>
       <c r="K100" s="4"/>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
@@ -3108,20 +3231,20 @@
       <c r="R100" s="4"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B101" s="15"/>
-      <c r="C101" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D101" s="15"/>
-      <c r="E101" s="15"/>
-      <c r="F101" s="15"/>
-      <c r="G101" s="15"/>
-      <c r="H101" s="15"/>
-      <c r="I101" s="15"/>
-      <c r="J101" s="4"/>
+      <c r="A101" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B101" s="13"/>
+      <c r="C101" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D101" s="13"/>
+      <c r="E101" s="13"/>
+      <c r="F101" s="13"/>
+      <c r="G101" s="13"/>
+      <c r="H101" s="13"/>
+      <c r="I101" s="13"/>
+      <c r="J101" s="13"/>
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
@@ -3132,20 +3255,20 @@
       <c r="R101" s="4"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="B102" s="15"/>
-      <c r="C102" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="D102" s="15"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="15"/>
-      <c r="G102" s="15"/>
-      <c r="H102" s="15"/>
-      <c r="I102" s="15"/>
-      <c r="J102" s="4"/>
+      <c r="A102" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B102" s="13"/>
+      <c r="C102" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D102" s="13"/>
+      <c r="E102" s="13"/>
+      <c r="F102" s="13"/>
+      <c r="G102" s="13"/>
+      <c r="H102" s="13"/>
+      <c r="I102" s="13"/>
+      <c r="J102" s="13"/>
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
@@ -3156,20 +3279,20 @@
       <c r="R102" s="4"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="B103" s="15"/>
-      <c r="C103" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D103" s="15"/>
-      <c r="E103" s="15"/>
-      <c r="F103" s="15"/>
-      <c r="G103" s="15"/>
-      <c r="H103" s="15"/>
-      <c r="I103" s="15"/>
-      <c r="J103" s="4"/>
+      <c r="A103" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B103" s="13"/>
+      <c r="C103" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="D103" s="13"/>
+      <c r="E103" s="13"/>
+      <c r="F103" s="13"/>
+      <c r="G103" s="13"/>
+      <c r="H103" s="13"/>
+      <c r="I103" s="13"/>
+      <c r="J103" s="13"/>
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="173">
   <si>
     <t xml:space="preserve">Project ID Number:</t>
   </si>
@@ -458,6 +458,9 @@
   </si>
   <si>
     <t xml:space="preserve">Does the basic HelloWorld firmware program and function properly?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Had to swap out the USB to UART bridge chip for a different part number</t>
   </si>
   <si>
     <t xml:space="preserve">SST 3</t>
@@ -980,7 +983,7 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="5" t="n">
-        <v>45662</v>
+        <v>45666</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="3"/>
@@ -2980,8 +2983,12 @@
       <c r="G90" s="13"/>
       <c r="H90" s="13"/>
       <c r="I90" s="13"/>
-      <c r="J90" s="13"/>
-      <c r="K90" s="4"/>
+      <c r="J90" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
       <c r="N90" s="4"/>
@@ -2992,11 +2999,11 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B91" s="13"/>
       <c r="C91" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D91" s="13"/>
       <c r="E91" s="13"/>
@@ -3004,7 +3011,9 @@
       <c r="G91" s="13"/>
       <c r="H91" s="13"/>
       <c r="I91" s="13"/>
-      <c r="J91" s="13"/>
+      <c r="J91" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="K91" s="4"/>
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
@@ -3016,11 +3025,11 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B92" s="13"/>
       <c r="C92" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D92" s="13"/>
       <c r="E92" s="13"/>
@@ -3040,11 +3049,11 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B93" s="13"/>
       <c r="C93" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D93" s="13"/>
       <c r="E93" s="13"/>
@@ -3064,11 +3073,11 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B94" s="13"/>
       <c r="C94" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D94" s="13"/>
       <c r="E94" s="13"/>
@@ -3088,11 +3097,11 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B95" s="13"/>
       <c r="C95" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D95" s="13"/>
       <c r="E95" s="13"/>
@@ -3112,11 +3121,11 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B96" s="13"/>
       <c r="C96" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D96" s="13"/>
       <c r="E96" s="13"/>
@@ -3136,11 +3145,11 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B97" s="13"/>
       <c r="C97" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D97" s="13"/>
       <c r="E97" s="13"/>
@@ -3160,11 +3169,11 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B98" s="13"/>
       <c r="C98" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D98" s="13"/>
       <c r="E98" s="13"/>
@@ -3184,11 +3193,11 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B99" s="13"/>
       <c r="C99" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="13"/>
@@ -3208,11 +3217,11 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B100" s="13"/>
       <c r="C100" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D100" s="13"/>
       <c r="E100" s="13"/>
@@ -3232,11 +3241,11 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B101" s="13"/>
       <c r="C101" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D101" s="13"/>
       <c r="E101" s="13"/>
@@ -3256,11 +3265,11 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B102" s="13"/>
       <c r="C102" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D102" s="13"/>
       <c r="E102" s="13"/>
@@ -3280,11 +3289,11 @@
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B103" s="13"/>
       <c r="C103" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D103" s="13"/>
       <c r="E103" s="13"/>

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="174">
   <si>
     <t xml:space="preserve">Project ID Number:</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t xml:space="preserve">PCB Serial Number:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3C54FC05-659A-3-1</t>
   </si>
   <si>
     <t xml:space="preserve">Tested By:</t>
@@ -651,7 +654,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -687,7 +690,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -936,7 +939,9 @@
         <v>4</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="4"/>
+      <c r="C3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="D3" s="4"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -955,11 +960,11 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="3"/>
@@ -979,7 +984,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="5" t="n">
@@ -1003,7 +1008,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
@@ -1065,7 +1070,7 @@
     </row>
     <row r="9" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -1087,31 +1092,31 @@
     </row>
     <row r="10" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" s="12"/>
       <c r="K10" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
@@ -1121,31 +1126,31 @@
     </row>
     <row r="11" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J11" s="12"/>
       <c r="K11" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L11" s="12"/>
       <c r="M11" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
@@ -1155,31 +1160,31 @@
     </row>
     <row r="12" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J12" s="12"/>
       <c r="K12" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L12" s="12"/>
       <c r="M12" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
@@ -1391,7 +1396,7 @@
     <row r="24" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
@@ -1413,11 +1418,11 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
@@ -1426,10 +1431,10 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
@@ -1440,190 +1445,190 @@
       <c r="R26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13" t="s">
+      <c r="A27" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13" t="s">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13" t="s">
+      <c r="A28" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13" t="s">
+      <c r="A29" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13" t="s">
+      <c r="A30" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="13"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13" t="s">
+      <c r="A31" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13" t="s">
+      <c r="A32" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13" t="s">
+      <c r="A33" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -1645,11 +1650,11 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -1658,10 +1663,10 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
       <c r="J37" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
@@ -1672,1230 +1677,1230 @@
       <c r="R37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13" t="s">
+      <c r="A38" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13" t="s">
+      <c r="A39" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="13"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13" t="s">
+      <c r="A40" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13"/>
+      <c r="P40" s="13"/>
+      <c r="Q40" s="13"/>
+      <c r="R40" s="13"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13" t="s">
+      <c r="A41" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13"/>
+      <c r="P41" s="13"/>
+      <c r="Q41" s="13"/>
+      <c r="R41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13" t="s">
+      <c r="A42" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+      <c r="M42" s="13"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13"/>
+      <c r="P42" s="13"/>
+      <c r="Q42" s="13"/>
+      <c r="R42" s="13"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13" t="s">
+      <c r="A43" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="13"/>
+      <c r="R43" s="13"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13" t="s">
+      <c r="A44" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13"/>
+      <c r="P44" s="13"/>
+      <c r="Q44" s="13"/>
+      <c r="R44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13" t="s">
+      <c r="A45" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K45" s="13"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
+      <c r="N45" s="13"/>
+      <c r="O45" s="13"/>
+      <c r="P45" s="13"/>
+      <c r="Q45" s="13"/>
+      <c r="R45" s="13"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13" t="s">
+      <c r="A46" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
+      <c r="P46" s="13"/>
+      <c r="Q46" s="13"/>
+      <c r="R46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13" t="s">
+      <c r="A47" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="13"/>
+      <c r="Q47" s="13"/>
+      <c r="R47" s="13"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13" t="s">
+      <c r="A48" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13"/>
+      <c r="P48" s="13"/>
+      <c r="Q48" s="13"/>
+      <c r="R48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13" t="s">
+      <c r="A49" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K49" s="13"/>
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13"/>
+      <c r="P49" s="13"/>
+      <c r="Q49" s="13"/>
+      <c r="R49" s="13"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="13"/>
+      <c r="Q50" s="13"/>
+      <c r="R50" s="13"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="13"/>
+      <c r="Q51" s="13"/>
+      <c r="R51" s="13"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13"/>
+      <c r="P52" s="13"/>
+      <c r="Q52" s="13"/>
+      <c r="R52" s="13"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="13" t="s">
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13"/>
+      <c r="P53" s="13"/>
+      <c r="Q53" s="13"/>
+      <c r="R53" s="13"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13"/>
+      <c r="P54" s="13"/>
+      <c r="Q54" s="13"/>
+      <c r="R54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13" t="s">
+      <c r="A55" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13"/>
+      <c r="P55" s="13"/>
+      <c r="Q55" s="13"/>
+      <c r="R55" s="13"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13" t="s">
+      <c r="A56" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K56" s="13"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13"/>
+      <c r="P56" s="13"/>
+      <c r="Q56" s="13"/>
+      <c r="R56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13" t="s">
+      <c r="A57" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="13"/>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13"/>
+      <c r="P57" s="13"/>
+      <c r="Q57" s="13"/>
+      <c r="R57" s="13"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13" t="s">
+      <c r="A58" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K58" s="13"/>
+      <c r="L58" s="13"/>
+      <c r="M58" s="13"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13"/>
+      <c r="P58" s="13"/>
+      <c r="Q58" s="13"/>
+      <c r="R58" s="13"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13" t="s">
+      <c r="A59" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
-      <c r="P59" s="4"/>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13"/>
+      <c r="P59" s="13"/>
+      <c r="Q59" s="13"/>
+      <c r="R59" s="13"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13" t="s">
+      <c r="A60" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="4"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13"/>
+      <c r="P60" s="13"/>
+      <c r="Q60" s="13"/>
+      <c r="R60" s="13"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13" t="s">
+      <c r="A61" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13"/>
+      <c r="P61" s="13"/>
+      <c r="Q61" s="13"/>
+      <c r="R61" s="13"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13" t="s">
+      <c r="A62" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13"/>
+      <c r="P62" s="13"/>
+      <c r="Q62" s="13"/>
+      <c r="R62" s="13"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B63" s="13"/>
-      <c r="C63" s="13" t="s">
+      <c r="A63" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="13"/>
-      <c r="J63" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="4"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K63" s="13"/>
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13"/>
+      <c r="P63" s="13"/>
+      <c r="Q63" s="13"/>
+      <c r="R63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B64" s="13"/>
-      <c r="C64" s="13" t="s">
+      <c r="A64" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="4"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K64" s="13"/>
+      <c r="L64" s="13"/>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13"/>
+      <c r="P64" s="13"/>
+      <c r="Q64" s="13"/>
+      <c r="R64" s="13"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="B65" s="13"/>
-      <c r="C65" s="13" t="s">
+      <c r="A65" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="13"/>
-      <c r="J65" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="4"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K65" s="13"/>
+      <c r="L65" s="13"/>
+      <c r="M65" s="13"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="13"/>
+      <c r="P65" s="13"/>
+      <c r="Q65" s="13"/>
+      <c r="R65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13" t="s">
+      <c r="A66" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13"/>
+      <c r="P66" s="13"/>
+      <c r="Q66" s="13"/>
+      <c r="R66" s="13"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B67" s="13"/>
-      <c r="C67" s="13" t="s">
+      <c r="A67" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K67" s="13"/>
+      <c r="L67" s="13"/>
+      <c r="M67" s="13"/>
+      <c r="N67" s="13"/>
+      <c r="O67" s="13"/>
+      <c r="P67" s="13"/>
+      <c r="Q67" s="13"/>
+      <c r="R67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13" t="s">
+      <c r="A68" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
-      <c r="P68" s="4"/>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K68" s="13"/>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="13"/>
+      <c r="P68" s="13"/>
+      <c r="Q68" s="13"/>
+      <c r="R68" s="13"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13" t="s">
+      <c r="A69" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K69" s="13"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+      <c r="N69" s="13"/>
+      <c r="O69" s="13"/>
+      <c r="P69" s="13"/>
+      <c r="Q69" s="13"/>
+      <c r="R69" s="13"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="B70" s="13"/>
-      <c r="C70" s="13" t="s">
+      <c r="A70" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4"/>
-      <c r="Q70" s="4"/>
-      <c r="R70" s="4"/>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K70" s="13"/>
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="13"/>
+      <c r="P70" s="13"/>
+      <c r="Q70" s="13"/>
+      <c r="R70" s="13"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13" t="s">
+      <c r="A71" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
-      <c r="Q71" s="4"/>
-      <c r="R71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K71" s="13"/>
+      <c r="L71" s="13"/>
+      <c r="M71" s="13"/>
+      <c r="N71" s="13"/>
+      <c r="O71" s="13"/>
+      <c r="P71" s="13"/>
+      <c r="Q71" s="13"/>
+      <c r="R71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13" t="s">
+      <c r="A72" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K72" s="13"/>
+      <c r="L72" s="13"/>
+      <c r="M72" s="13"/>
+      <c r="N72" s="13"/>
+      <c r="O72" s="13"/>
+      <c r="P72" s="13"/>
+      <c r="Q72" s="13"/>
+      <c r="R72" s="13"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B73" s="13"/>
-      <c r="C73" s="13" t="s">
+      <c r="A73" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K73" s="4"/>
-      <c r="L73" s="4"/>
-      <c r="M73" s="4"/>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K73" s="13"/>
+      <c r="L73" s="13"/>
+      <c r="M73" s="13"/>
+      <c r="N73" s="13"/>
+      <c r="O73" s="13"/>
+      <c r="P73" s="13"/>
+      <c r="Q73" s="13"/>
+      <c r="R73" s="13"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13" t="s">
+      <c r="A74" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
-      <c r="N74" s="4"/>
-      <c r="O74" s="4"/>
-      <c r="P74" s="4"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K74" s="13"/>
+      <c r="L74" s="13"/>
+      <c r="M74" s="13"/>
+      <c r="N74" s="13"/>
+      <c r="O74" s="13"/>
+      <c r="P74" s="13"/>
+      <c r="Q74" s="13"/>
+      <c r="R74" s="13"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13" t="s">
+      <c r="A75" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
-      <c r="J75" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K75" s="4"/>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-      <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K75" s="13"/>
+      <c r="L75" s="13"/>
+      <c r="M75" s="13"/>
+      <c r="N75" s="13"/>
+      <c r="O75" s="13"/>
+      <c r="P75" s="13"/>
+      <c r="Q75" s="13"/>
+      <c r="R75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13" t="s">
+      <c r="A76" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
-      <c r="J76" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
-      <c r="O76" s="4"/>
-      <c r="P76" s="4"/>
-      <c r="Q76" s="4"/>
-      <c r="R76" s="4"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K76" s="13"/>
+      <c r="L76" s="13"/>
+      <c r="M76" s="13"/>
+      <c r="N76" s="13"/>
+      <c r="O76" s="13"/>
+      <c r="P76" s="13"/>
+      <c r="Q76" s="13"/>
+      <c r="R76" s="13"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="B77" s="13"/>
-      <c r="C77" s="13" t="s">
+      <c r="A77" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
-      <c r="J77" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4"/>
-      <c r="O77" s="4"/>
-      <c r="P77" s="4"/>
-      <c r="Q77" s="4"/>
-      <c r="R77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K77" s="13"/>
+      <c r="L77" s="13"/>
+      <c r="M77" s="13"/>
+      <c r="N77" s="13"/>
+      <c r="O77" s="13"/>
+      <c r="P77" s="13"/>
+      <c r="Q77" s="13"/>
+      <c r="R77" s="13"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13" t="s">
+      <c r="A78" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-      <c r="J78" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
-      <c r="O78" s="4"/>
-      <c r="P78" s="4"/>
-      <c r="Q78" s="4"/>
-      <c r="R78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K78" s="13"/>
+      <c r="L78" s="13"/>
+      <c r="M78" s="13"/>
+      <c r="N78" s="13"/>
+      <c r="O78" s="13"/>
+      <c r="P78" s="13"/>
+      <c r="Q78" s="13"/>
+      <c r="R78" s="13"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B79" s="13"/>
-      <c r="C79" s="13" t="s">
+      <c r="A79" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
-      <c r="J79" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="4"/>
-      <c r="N79" s="4"/>
-      <c r="O79" s="4"/>
-      <c r="P79" s="4"/>
-      <c r="Q79" s="4"/>
-      <c r="R79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K79" s="13"/>
+      <c r="L79" s="13"/>
+      <c r="M79" s="13"/>
+      <c r="N79" s="13"/>
+      <c r="O79" s="13"/>
+      <c r="P79" s="13"/>
+      <c r="Q79" s="13"/>
+      <c r="R79" s="13"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B80" s="13"/>
-      <c r="C80" s="13" t="s">
+      <c r="A80" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
-      <c r="J80" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K80" s="4"/>
-      <c r="L80" s="4"/>
-      <c r="M80" s="4"/>
-      <c r="N80" s="4"/>
-      <c r="O80" s="4"/>
-      <c r="P80" s="4"/>
-      <c r="Q80" s="4"/>
-      <c r="R80" s="4"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K80" s="13"/>
+      <c r="L80" s="13"/>
+      <c r="M80" s="13"/>
+      <c r="N80" s="13"/>
+      <c r="O80" s="13"/>
+      <c r="P80" s="13"/>
+      <c r="Q80" s="13"/>
+      <c r="R80" s="13"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B81" s="13"/>
-      <c r="C81" s="13" t="s">
+      <c r="A81" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
-      <c r="H81" s="13"/>
-      <c r="I81" s="13"/>
-      <c r="J81" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K81" s="4"/>
-      <c r="L81" s="4"/>
-      <c r="M81" s="4"/>
-      <c r="N81" s="4"/>
-      <c r="O81" s="4"/>
-      <c r="P81" s="4"/>
-      <c r="Q81" s="4"/>
-      <c r="R81" s="4"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K81" s="13"/>
+      <c r="L81" s="13"/>
+      <c r="M81" s="13"/>
+      <c r="N81" s="13"/>
+      <c r="O81" s="13"/>
+      <c r="P81" s="13"/>
+      <c r="Q81" s="13"/>
+      <c r="R81" s="13"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B82" s="13"/>
-      <c r="C82" s="13" t="s">
+      <c r="A82" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
-      <c r="H82" s="13"/>
-      <c r="I82" s="13"/>
-      <c r="J82" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K82" s="4"/>
-      <c r="L82" s="4"/>
-      <c r="M82" s="4"/>
-      <c r="N82" s="4"/>
-      <c r="O82" s="4"/>
-      <c r="P82" s="4"/>
-      <c r="Q82" s="4"/>
-      <c r="R82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K82" s="13"/>
+      <c r="L82" s="13"/>
+      <c r="M82" s="13"/>
+      <c r="N82" s="13"/>
+      <c r="O82" s="13"/>
+      <c r="P82" s="13"/>
+      <c r="Q82" s="13"/>
+      <c r="R82" s="13"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B83" s="13"/>
-      <c r="C83" s="13" t="s">
+      <c r="A83" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K83" s="4"/>
-      <c r="L83" s="4"/>
-      <c r="M83" s="4"/>
-      <c r="N83" s="4"/>
-      <c r="O83" s="4"/>
-      <c r="P83" s="4"/>
-      <c r="Q83" s="4"/>
-      <c r="R83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K83" s="13"/>
+      <c r="L83" s="13"/>
+      <c r="M83" s="13"/>
+      <c r="N83" s="13"/>
+      <c r="O83" s="13"/>
+      <c r="P83" s="13"/>
+      <c r="Q83" s="13"/>
+      <c r="R83" s="13"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13" t="s">
+      <c r="A84" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K84" s="4"/>
-      <c r="L84" s="4"/>
-      <c r="M84" s="4"/>
-      <c r="N84" s="4"/>
-      <c r="O84" s="4"/>
-      <c r="P84" s="4"/>
-      <c r="Q84" s="4"/>
-      <c r="R84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K84" s="13"/>
+      <c r="L84" s="13"/>
+      <c r="M84" s="13"/>
+      <c r="N84" s="13"/>
+      <c r="O84" s="13"/>
+      <c r="P84" s="13"/>
+      <c r="Q84" s="13"/>
+      <c r="R84" s="13"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -2917,11 +2922,11 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B88" s="11"/>
       <c r="C88" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D88" s="11"/>
       <c r="E88" s="11"/>
@@ -2930,10 +2935,10 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
       <c r="J88" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K88" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L88" s="11"/>
       <c r="M88" s="11"/>
@@ -2944,372 +2949,372 @@
       <c r="R88" s="11"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="B89" s="13"/>
-      <c r="C89" s="13" t="s">
+      <c r="A89" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="13"/>
-      <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
-      <c r="J89" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K89" s="4"/>
-      <c r="L89" s="4"/>
-      <c r="M89" s="4"/>
-      <c r="N89" s="4"/>
-      <c r="O89" s="4"/>
-      <c r="P89" s="4"/>
-      <c r="Q89" s="4"/>
-      <c r="R89" s="4"/>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K89" s="13"/>
+      <c r="L89" s="13"/>
+      <c r="M89" s="13"/>
+      <c r="N89" s="13"/>
+      <c r="O89" s="13"/>
+      <c r="P89" s="13"/>
+      <c r="Q89" s="13"/>
+      <c r="R89" s="13"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="B90" s="13"/>
-      <c r="C90" s="13" t="s">
+      <c r="A90" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
-      <c r="J90" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K90" s="4" t="s">
+      <c r="B90" s="4"/>
+      <c r="C90" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="L90" s="4"/>
-      <c r="M90" s="4"/>
-      <c r="N90" s="4"/>
-      <c r="O90" s="4"/>
-      <c r="P90" s="4"/>
-      <c r="Q90" s="4"/>
-      <c r="R90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K90" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="L90" s="13"/>
+      <c r="M90" s="13"/>
+      <c r="N90" s="13"/>
+      <c r="O90" s="13"/>
+      <c r="P90" s="13"/>
+      <c r="Q90" s="13"/>
+      <c r="R90" s="13"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="B91" s="13"/>
-      <c r="C91" s="13" t="s">
+      <c r="A91" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="13"/>
-      <c r="H91" s="13"/>
-      <c r="I91" s="13"/>
-      <c r="J91" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-      <c r="Q91" s="4"/>
-      <c r="R91" s="4"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K91" s="13"/>
+      <c r="L91" s="13"/>
+      <c r="M91" s="13"/>
+      <c r="N91" s="13"/>
+      <c r="O91" s="13"/>
+      <c r="P91" s="13"/>
+      <c r="Q91" s="13"/>
+      <c r="R91" s="13"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="B92" s="13"/>
-      <c r="C92" s="13" t="s">
+      <c r="A92" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D92" s="13"/>
-      <c r="E92" s="13"/>
-      <c r="F92" s="13"/>
-      <c r="G92" s="13"/>
-      <c r="H92" s="13"/>
-      <c r="I92" s="13"/>
-      <c r="J92" s="13"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-      <c r="Q92" s="4"/>
-      <c r="R92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="13"/>
+      <c r="L92" s="13"/>
+      <c r="M92" s="13"/>
+      <c r="N92" s="13"/>
+      <c r="O92" s="13"/>
+      <c r="P92" s="13"/>
+      <c r="Q92" s="13"/>
+      <c r="R92" s="13"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="B93" s="13"/>
-      <c r="C93" s="13" t="s">
+      <c r="A93" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="13"/>
-      <c r="H93" s="13"/>
-      <c r="I93" s="13"/>
-      <c r="J93" s="13"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="4"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="13"/>
+      <c r="L93" s="13"/>
+      <c r="M93" s="13"/>
+      <c r="N93" s="13"/>
+      <c r="O93" s="13"/>
+      <c r="P93" s="13"/>
+      <c r="Q93" s="13"/>
+      <c r="R93" s="13"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="B94" s="13"/>
-      <c r="C94" s="13" t="s">
+      <c r="A94" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="13"/>
-      <c r="J94" s="13"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="13"/>
+      <c r="L94" s="13"/>
+      <c r="M94" s="13"/>
+      <c r="N94" s="13"/>
+      <c r="O94" s="13"/>
+      <c r="P94" s="13"/>
+      <c r="Q94" s="13"/>
+      <c r="R94" s="13"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="B95" s="13"/>
-      <c r="C95" s="13" t="s">
+      <c r="A95" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="13"/>
-      <c r="H95" s="13"/>
-      <c r="I95" s="13"/>
-      <c r="J95" s="13"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
-      <c r="Q95" s="4"/>
-      <c r="R95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="13"/>
+      <c r="L95" s="13"/>
+      <c r="M95" s="13"/>
+      <c r="N95" s="13"/>
+      <c r="O95" s="13"/>
+      <c r="P95" s="13"/>
+      <c r="Q95" s="13"/>
+      <c r="R95" s="13"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="B96" s="13"/>
-      <c r="C96" s="13" t="s">
+      <c r="A96" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
-      <c r="I96" s="13"/>
-      <c r="J96" s="13"/>
-      <c r="K96" s="4"/>
-      <c r="L96" s="4"/>
-      <c r="M96" s="4"/>
-      <c r="N96" s="4"/>
-      <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
-      <c r="Q96" s="4"/>
-      <c r="R96" s="4"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="13"/>
+      <c r="L96" s="13"/>
+      <c r="M96" s="13"/>
+      <c r="N96" s="13"/>
+      <c r="O96" s="13"/>
+      <c r="P96" s="13"/>
+      <c r="Q96" s="13"/>
+      <c r="R96" s="13"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="B97" s="13"/>
-      <c r="C97" s="13" t="s">
+      <c r="A97" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D97" s="13"/>
-      <c r="E97" s="13"/>
-      <c r="F97" s="13"/>
-      <c r="G97" s="13"/>
-      <c r="H97" s="13"/>
-      <c r="I97" s="13"/>
-      <c r="J97" s="13"/>
-      <c r="K97" s="4"/>
-      <c r="L97" s="4"/>
-      <c r="M97" s="4"/>
-      <c r="N97" s="4"/>
-      <c r="O97" s="4"/>
-      <c r="P97" s="4"/>
-      <c r="Q97" s="4"/>
-      <c r="R97" s="4"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="13"/>
+      <c r="L97" s="13"/>
+      <c r="M97" s="13"/>
+      <c r="N97" s="13"/>
+      <c r="O97" s="13"/>
+      <c r="P97" s="13"/>
+      <c r="Q97" s="13"/>
+      <c r="R97" s="13"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13" t="s">
+      <c r="A98" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
-      <c r="H98" s="13"/>
-      <c r="I98" s="13"/>
-      <c r="J98" s="13"/>
-      <c r="K98" s="4"/>
-      <c r="L98" s="4"/>
-      <c r="M98" s="4"/>
-      <c r="N98" s="4"/>
-      <c r="O98" s="4"/>
-      <c r="P98" s="4"/>
-      <c r="Q98" s="4"/>
-      <c r="R98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="13"/>
+      <c r="L98" s="13"/>
+      <c r="M98" s="13"/>
+      <c r="N98" s="13"/>
+      <c r="O98" s="13"/>
+      <c r="P98" s="13"/>
+      <c r="Q98" s="13"/>
+      <c r="R98" s="13"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B99" s="13"/>
-      <c r="C99" s="13" t="s">
+      <c r="A99" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
-      <c r="H99" s="13"/>
-      <c r="I99" s="13"/>
-      <c r="J99" s="13"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="4"/>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4"/>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
-      <c r="Q99" s="4"/>
-      <c r="R99" s="4"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="13"/>
+      <c r="L99" s="13"/>
+      <c r="M99" s="13"/>
+      <c r="N99" s="13"/>
+      <c r="O99" s="13"/>
+      <c r="P99" s="13"/>
+      <c r="Q99" s="13"/>
+      <c r="R99" s="13"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B100" s="13"/>
-      <c r="C100" s="13" t="s">
+      <c r="A100" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
-      <c r="H100" s="13"/>
-      <c r="I100" s="13"/>
-      <c r="J100" s="13"/>
-      <c r="K100" s="4"/>
-      <c r="L100" s="4"/>
-      <c r="M100" s="4"/>
-      <c r="N100" s="4"/>
-      <c r="O100" s="4"/>
-      <c r="P100" s="4"/>
-      <c r="Q100" s="4"/>
-      <c r="R100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="13"/>
+      <c r="L100" s="13"/>
+      <c r="M100" s="13"/>
+      <c r="N100" s="13"/>
+      <c r="O100" s="13"/>
+      <c r="P100" s="13"/>
+      <c r="Q100" s="13"/>
+      <c r="R100" s="13"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="B101" s="13"/>
-      <c r="C101" s="13" t="s">
+      <c r="A101" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="D101" s="13"/>
-      <c r="E101" s="13"/>
-      <c r="F101" s="13"/>
-      <c r="G101" s="13"/>
-      <c r="H101" s="13"/>
-      <c r="I101" s="13"/>
-      <c r="J101" s="13"/>
-      <c r="K101" s="4"/>
-      <c r="L101" s="4"/>
-      <c r="M101" s="4"/>
-      <c r="N101" s="4"/>
-      <c r="O101" s="4"/>
-      <c r="P101" s="4"/>
-      <c r="Q101" s="4"/>
-      <c r="R101" s="4"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="13"/>
+      <c r="L101" s="13"/>
+      <c r="M101" s="13"/>
+      <c r="N101" s="13"/>
+      <c r="O101" s="13"/>
+      <c r="P101" s="13"/>
+      <c r="Q101" s="13"/>
+      <c r="R101" s="13"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="B102" s="13"/>
-      <c r="C102" s="13" t="s">
+      <c r="A102" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="13"/>
-      <c r="H102" s="13"/>
-      <c r="I102" s="13"/>
-      <c r="J102" s="13"/>
-      <c r="K102" s="4"/>
-      <c r="L102" s="4"/>
-      <c r="M102" s="4"/>
-      <c r="N102" s="4"/>
-      <c r="O102" s="4"/>
-      <c r="P102" s="4"/>
-      <c r="Q102" s="4"/>
-      <c r="R102" s="4"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="13"/>
+      <c r="L102" s="13"/>
+      <c r="M102" s="13"/>
+      <c r="N102" s="13"/>
+      <c r="O102" s="13"/>
+      <c r="P102" s="13"/>
+      <c r="Q102" s="13"/>
+      <c r="R102" s="13"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B103" s="13"/>
-      <c r="C103" s="13" t="s">
+      <c r="A103" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D103" s="13"/>
-      <c r="E103" s="13"/>
-      <c r="F103" s="13"/>
-      <c r="G103" s="13"/>
-      <c r="H103" s="13"/>
-      <c r="I103" s="13"/>
-      <c r="J103" s="13"/>
-      <c r="K103" s="4"/>
-      <c r="L103" s="4"/>
-      <c r="M103" s="4"/>
-      <c r="N103" s="4"/>
-      <c r="O103" s="4"/>
-      <c r="P103" s="4"/>
-      <c r="Q103" s="4"/>
-      <c r="R103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="13"/>
+      <c r="L103" s="13"/>
+      <c r="M103" s="13"/>
+      <c r="N103" s="13"/>
+      <c r="O103" s="13"/>
+      <c r="P103" s="13"/>
+      <c r="Q103" s="13"/>
+      <c r="R103" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="325">

--- a/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
+++ b/_Projects/P1012202501-ESP32_Stepper_Controller/ProjectDocuments/test-logs/P1012202501-01 Test Plan Log.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="177">
   <si>
     <t xml:space="preserve">Project ID Number:</t>
   </si>
@@ -52,6 +52,9 @@
     <t xml:space="preserve">Overall Test Result:</t>
   </si>
   <si>
+    <t xml:space="preserve">Pass</t>
+  </si>
+  <si>
     <t xml:space="preserve">Test Equipment Log</t>
   </si>
   <si>
@@ -103,6 +106,12 @@
     <t xml:space="preserve">SPE610224121294</t>
   </si>
   <si>
+    <t xml:space="preserve">IR Thermometer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXTECH</t>
+  </si>
+  <si>
     <t xml:space="preserve">Functional Requirements Checklist</t>
   </si>
   <si>
@@ -124,9 +133,6 @@
     <t xml:space="preserve">ESP32 module with Wi‑Fi and BLE support</t>
   </si>
   <si>
-    <t xml:space="preserve">Pass</t>
-  </si>
-  <si>
     <t xml:space="preserve">FR-002</t>
   </si>
   <si>
@@ -542,6 +548,9 @@
   </si>
   <si>
     <t xml:space="preserve">Does the temperature sensor operate properly?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added 100nF cap between TEMP_SENSE line and GND to help filter noise on the ESP32</t>
   </si>
 </sst>
 </file>
@@ -988,7 +997,7 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="5" t="n">
-        <v>45666</v>
+        <v>46040</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="3"/>
@@ -1011,7 +1020,9 @@
         <v>9</v>
       </c>
       <c r="B6" s="1"/>
-      <c r="C6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="D6" s="2"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1070,7 +1081,7 @@
     </row>
     <row r="9" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -1092,31 +1103,31 @@
     </row>
     <row r="10" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" s="12"/>
       <c r="K10" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
@@ -1126,31 +1137,31 @@
     </row>
     <row r="11" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J11" s="12"/>
       <c r="K11" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L11" s="12"/>
       <c r="M11" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
@@ -1160,31 +1171,31 @@
     </row>
     <row r="12" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J12" s="12"/>
       <c r="K12" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L12" s="12"/>
       <c r="M12" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
@@ -1193,19 +1204,33 @@
       <c r="R12" s="12"/>
     </row>
     <row r="13" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11"/>
+      <c r="A13" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
+      <c r="C13" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="D13" s="11"/>
-      <c r="E13" s="12"/>
+      <c r="E13" s="12" t="n">
+        <v>42520</v>
+      </c>
       <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+      <c r="G13" s="12" t="n">
+        <v>9002511</v>
+      </c>
       <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
+      <c r="I13" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
+      <c r="K13" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
+      <c r="M13" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
@@ -1396,7 +1421,7 @@
     <row r="24" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
@@ -1418,11 +1443,11 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
@@ -1431,10 +1456,10 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
@@ -1446,11 +1471,11 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -1459,7 +1484,7 @@
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
@@ -1472,11 +1497,11 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -1485,7 +1510,7 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
@@ -1498,11 +1523,11 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -1511,7 +1536,7 @@
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
@@ -1524,11 +1549,11 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -1537,7 +1562,7 @@
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K30" s="13"/>
       <c r="L30" s="13"/>
@@ -1550,11 +1575,11 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -1563,7 +1588,7 @@
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K31" s="13"/>
       <c r="L31" s="13"/>
@@ -1576,11 +1601,11 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -1589,7 +1614,7 @@
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K32" s="13"/>
       <c r="L32" s="13"/>
@@ -1602,11 +1627,11 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -1615,7 +1640,7 @@
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K33" s="13"/>
       <c r="L33" s="13"/>
@@ -1628,7 +1653,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -1650,11 +1675,11 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -1663,10 +1688,10 @@
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
       <c r="J37" s="11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
@@ -1678,11 +1703,11 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -1691,7 +1716,7 @@
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K38" s="13"/>
       <c r="L38" s="13"/>
@@ -1704,11 +1729,11 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -1717,7 +1742,7 @@
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K39" s="13"/>
       <c r="L39" s="13"/>
@@ -1730,11 +1755,11 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -1743,7 +1768,7 @@
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K40" s="13"/>
       <c r="L40" s="13"/>
@@ -1756,11 +1781,11 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -1769,7 +1794,7 @@
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K41" s="13"/>
       <c r="L41" s="13"/>
@@ -1782,11 +1807,11 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -1795,7 +1820,7 @@
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K42" s="13"/>
       <c r="L42" s="13"/>
@@ -1808,11 +1833,11 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -1821,7 +1846,7 @@
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K43" s="13"/>
       <c r="L43" s="13"/>
@@ -1834,11 +1859,11 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -1847,7 +1872,7 @@
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K44" s="13"/>
       <c r="L44" s="13"/>
@@ -1860,11 +1885,11 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -1873,7 +1898,7 @@
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K45" s="13"/>
       <c r="L45" s="13"/>
@@ -1886,11 +1911,11 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -1899,7 +1924,7 @@
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K46" s="13"/>
       <c r="L46" s="13"/>
@@ -1912,11 +1937,11 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -1925,7 +1950,7 @@
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K47" s="13"/>
       <c r="L47" s="13"/>
@@ -1938,11 +1963,11 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -1951,7 +1976,7 @@
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K48" s="13"/>
       <c r="L48" s="13"/>
@@ -1964,11 +1989,11 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -1977,7 +2002,7 @@
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K49" s="13"/>
       <c r="L49" s="13"/>
@@ -1990,11 +2015,11 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -2003,7 +2028,7 @@
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K50" s="13"/>
       <c r="L50" s="13"/>
@@ -2016,11 +2041,11 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -2029,7 +2054,7 @@
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K51" s="13"/>
       <c r="L51" s="13"/>
@@ -2042,11 +2067,11 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -2055,7 +2080,7 @@
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K52" s="13"/>
       <c r="L52" s="13"/>
@@ -2068,11 +2093,11 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -2081,7 +2106,7 @@
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K53" s="13"/>
       <c r="L53" s="13"/>
@@ -2094,11 +2119,11 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -2107,7 +2132,7 @@
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K54" s="13"/>
       <c r="L54" s="13"/>
@@ -2120,11 +2145,11 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -2133,7 +2158,7 @@
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K55" s="13"/>
       <c r="L55" s="13"/>
@@ -2146,11 +2171,11 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -2159,7 +2184,7 @@
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K56" s="13"/>
       <c r="L56" s="13"/>
@@ -2172,11 +2197,11 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -2185,7 +2210,7 @@
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K57" s="13"/>
       <c r="L57" s="13"/>
@@ -2198,11 +2223,11 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -2211,7 +2236,7 @@
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K58" s="13"/>
       <c r="L58" s="13"/>
@@ -2224,11 +2249,11 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -2237,7 +2262,7 @@
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
@@ -2250,11 +2275,11 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -2263,7 +2288,7 @@
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
@@ -2276,11 +2301,11 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -2289,7 +2314,7 @@
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
@@ -2302,11 +2327,11 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -2315,7 +2340,7 @@
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
@@ -2328,11 +2353,11 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -2341,7 +2366,7 @@
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
@@ -2354,11 +2379,11 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -2367,7 +2392,7 @@
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K64" s="13"/>
       <c r="L64" s="13"/>
@@ -2380,11 +2405,11 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -2393,7 +2418,7 @@
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
       <c r="J65" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K65" s="13"/>
       <c r="L65" s="13"/>
@@ -2406,11 +2431,11 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -2419,7 +2444,7 @@
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
       <c r="J66" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
@@ -2432,11 +2457,11 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -2445,7 +2470,7 @@
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
@@ -2458,11 +2483,11 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -2471,7 +2496,7 @@
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
@@ -2484,11 +2509,11 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -2497,7 +2522,7 @@
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K69" s="13"/>
       <c r="L69" s="13"/>
@@ -2510,11 +2535,11 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -2523,7 +2548,7 @@
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
       <c r="J70" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
@@ -2536,11 +2561,11 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -2549,7 +2574,7 @@
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
@@ -2562,11 +2587,11 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -2575,7 +2600,7 @@
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
       <c r="J72" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
@@ -2588,11 +2613,11 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
@@ -2601,7 +2626,7 @@
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K73" s="13"/>
       <c r="L73" s="13"/>
@@ -2614,11 +2639,11 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -2627,7 +2652,7 @@
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
@@ -2640,11 +2665,11 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
@@ -2653,7 +2678,7 @@
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
       <c r="J75" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
@@ -2666,11 +2691,11 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -2679,7 +2704,7 @@
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
       <c r="J76" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
@@ -2692,11 +2717,11 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -2705,7 +2730,7 @@
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
       <c r="J77" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K77" s="13"/>
       <c r="L77" s="13"/>
@@ -2718,11 +2743,11 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
@@ -2731,7 +2756,7 @@
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K78" s="13"/>
       <c r="L78" s="13"/>
@@ -2744,11 +2769,11 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -2757,7 +2782,7 @@
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
       <c r="J79" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K79" s="13"/>
       <c r="L79" s="13"/>
@@ -2770,11 +2795,11 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -2783,7 +2808,7 @@
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
       <c r="J80" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K80" s="13"/>
       <c r="L80" s="13"/>
@@ -2796,11 +2821,11 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -2809,7 +2834,7 @@
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
       <c r="J81" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K81" s="13"/>
       <c r="L81" s="13"/>
@@ -2822,11 +2847,11 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -2835,7 +2860,7 @@
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
       <c r="J82" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K82" s="13"/>
       <c r="L82" s="13"/>
@@ -2848,11 +2873,11 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -2861,7 +2886,7 @@
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
       <c r="J83" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K83" s="13"/>
       <c r="L83" s="13"/>
@@ -2874,11 +2899,11 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -2887,7 +2912,7 @@
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
       <c r="J84" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K84" s="13"/>
       <c r="L84" s="13"/>
@@ -2900,7 +2925,7 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -2922,11 +2947,11 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B88" s="11"/>
       <c r="C88" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D88" s="11"/>
       <c r="E88" s="11"/>
@@ -2935,10 +2960,10 @@
       <c r="H88" s="11"/>
       <c r="I88" s="11"/>
       <c r="J88" s="11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K88" s="11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L88" s="11"/>
       <c r="M88" s="11"/>
@@ -2950,11 +2975,11 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -2963,7 +2988,7 @@
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
       <c r="J89" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K89" s="13"/>
       <c r="L89" s="13"/>
@@ -2976,11 +3001,11 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -2989,10 +3014,10 @@
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
       <c r="J90" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K90" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L90" s="13"/>
       <c r="M90" s="13"/>
@@ -3004,11 +3029,11 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -3017,7 +3042,7 @@
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
       <c r="J91" s="4" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K91" s="13"/>
       <c r="L91" s="13"/>
@@ -3030,11 +3055,11 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -3042,7 +3067,9 @@
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
+      <c r="J92" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="K92" s="13"/>
       <c r="L92" s="13"/>
       <c r="M92" s="13"/>
@@ -3054,11 +3081,11 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -3066,7 +3093,9 @@
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
+      <c r="J93" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="K93" s="13"/>
       <c r="L93" s="13"/>
       <c r="M93" s="13"/>
@@ -3078,11 +3107,11 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
@@ -3090,7 +3119,9 @@
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
+      <c r="J94" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="K94" s="13"/>
       <c r="L94" s="13"/>
       <c r="M94" s="13"/>
@@ -3102,11 +3133,11 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -3114,7 +3145,9 @@
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
+      <c r="J95" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="K95" s="13"/>
       <c r="L95" s="13"/>
       <c r="M95" s="13"/>
@@ -3126,11 +3159,11 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -3138,7 +3171,9 @@
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
+      <c r="J96" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="K96" s="13"/>
       <c r="L96" s="13"/>
       <c r="M96" s="13"/>
@@ -3150,11 +3185,11 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -3162,7 +3197,9 @@
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
+      <c r="J97" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="K97" s="13"/>
       <c r="L97" s="13"/>
       <c r="M97" s="13"/>
@@ -3174,11 +3211,11 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
@@ -3186,7 +3223,9 @@
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
+      <c r="J98" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="K98" s="13"/>
       <c r="L98" s="13"/>
       <c r="M98" s="13"/>
@@ -3198,11 +3237,11 @@
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -3210,7 +3249,9 @@
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
+      <c r="J99" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="K99" s="13"/>
       <c r="L99" s="13"/>
       <c r="M99" s="13"/>
@@ -3222,11 +3263,11 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -3234,7 +3275,9 @@
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
+      <c r="J100" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="K100" s="13"/>
       <c r="L100" s="13"/>
       <c r="M100" s="13"/>
@@ -3246,11 +3289,11 @@
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -3258,7 +3301,9 @@
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
+      <c r="J101" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="K101" s="13"/>
       <c r="L101" s="13"/>
       <c r="M101" s="13"/>
@@ -3270,11 +3315,11 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -3282,7 +3327,9 @@
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
+      <c r="J102" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="K102" s="13"/>
       <c r="L102" s="13"/>
       <c r="M102" s="13"/>
@@ -3294,11 +3341,11 @@
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -3306,8 +3353,12 @@
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
-      <c r="J103" s="4"/>
-      <c r="K103" s="13"/>
+      <c r="J103" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K103" s="13" t="s">
+        <v>176</v>
+      </c>
       <c r="L103" s="13"/>
       <c r="M103" s="13"/>
       <c r="N103" s="13"/>
